--- a/templates/ENG/country_data.xlsx
+++ b/templates/ENG/country_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5aee5c5b004427f/Documents/mr-risk-assessment/templates/ENG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{5421454B-24A0-CB47-A2BC-441F244F2439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F023E9DA-B969-4EAE-B8A0-D18BD2D71545}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{5421454B-24A0-CB47-A2BC-441F244F2439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A1F747A-60C9-421E-BDFF-605FE2DE6FB6}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="773" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -570,9 +570,6 @@
     <t>Presence of areas with mass gatherings (e.g., trade/commerce, fairs, markets, sporting events, religious events)</t>
   </si>
   <si>
-    <t>Presence of rapid response team</t>
-  </si>
-  <si>
     <t>Fill in the data table below according to the following requirements:</t>
   </si>
   <si>
@@ -639,7 +636,10 @@
     <t>Value</t>
   </si>
   <si>
-    <t>Subnational areas with a team that has been trained in outbreak response in the last 2 years</t>
+    <t>Subnational areas with a team that has been trained in outbreak response in the last 2 years (Yes/No)</t>
+  </si>
+  <si>
+    <t>Presence of rapid response team (Yes/No)</t>
   </si>
 </sst>
 </file>
@@ -2629,7 +2629,7 @@
         <v>30</v>
       </c>
       <c r="B1" s="49" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -3442,7 +3442,7 @@
       <c r="D1" s="6"/>
       <c r="E1" s="9"/>
       <c r="F1" s="60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G1" s="61"/>
       <c r="H1" s="61"/>
@@ -3465,7 +3465,7 @@
       <c r="D2" s="6"/>
       <c r="E2" s="6"/>
       <c r="F2" s="58" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
@@ -3491,7 +3491,7 @@
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
       <c r="F3" s="63" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G3" s="62"/>
       <c r="H3" s="62"/>
@@ -3514,7 +3514,7 @@
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="F4" s="58" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
@@ -3537,7 +3537,7 @@
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
       <c r="F5" s="58" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G5" s="62"/>
       <c r="H5" s="62"/>
@@ -3560,7 +3560,7 @@
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G6" s="59"/>
       <c r="H6" s="59"/>
@@ -3641,43 +3641,43 @@
     </row>
     <row r="10" spans="1:19">
       <c r="A10" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="D10" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="E10" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="15" t="s">
+      <c r="F10" s="16" t="s">
         <v>79</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>80</v>
       </c>
       <c r="G10" s="15" t="s">
         <v>29</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K10" s="15" t="s">
         <v>29</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N10" s="15" t="s">
         <v>29</v>
@@ -3703,7 +3703,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>1</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>13</v>
@@ -3724,37 +3724,37 @@
         <v>4</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="K11" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="M11" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="N11" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="N11" s="3" t="s">
+      <c r="O11" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="O11" s="3" t="s">
+      <c r="P11" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="P11" s="3" t="s">
+      <c r="Q11" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="R11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4480,10 +4480,10 @@
         <v>51</v>
       </c>
       <c r="E1" s="52" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="F1" s="52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4693,12 +4693,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -4707,7 +4701,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007C69FE739999C447A76F1EF8B3FD66E4" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cbd048430c8551c34c2c3c8571f1b260">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="4655c133-e14e-4d88-8fbc-c3b347145ec5" xmlns:ns4="64ced670-a384-4657-ba0f-fc07d30f5a44" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5457dbb80d17598a17de4d439e456cf2" ns3:_="" ns4:_="">
     <xsd:import namespace="4655c133-e14e-4d88-8fbc-c3b347145ec5"/>
@@ -4930,24 +4924,13 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A51E5E2-41F2-4A1F-A4B0-950DEDB4B143}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4655c133-e14e-4d88-8fbc-c3b347145ec5"/>
-    <ds:schemaRef ds:uri="64ced670-a384-4657-ba0f-fc07d30f5a44"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6264E33-6917-4678-8EC8-8D88A2F9795C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -4955,7 +4938,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1C9E008-75C3-4280-8CCC-7498B59407BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4972,4 +4955,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A51E5E2-41F2-4A1F-A4B0-950DEDB4B143}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4655c133-e14e-4d88-8fbc-c3b347145ec5"/>
+    <ds:schemaRef ds:uri="64ced670-a384-4657-ba0f-fc07d30f5a44"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>